--- a/Ft-Cloud/ft-services/ft-service-pm/src/main/resources/template/importOrg.xlsx
+++ b/Ft-Cloud/ft-services/ft-service-pm/src/main/resources/template/importOrg.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="30240" windowHeight="13860"/>
+    <workbookView windowHeight="24320"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -14,15 +14,18 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t>序号</t>
   </si>
   <si>
-    <t>措施项</t>
-  </si>
-  <si>
-    <t>具体措施</t>
+    <t>组织架构</t>
+  </si>
+  <si>
+    <t>部门职责</t>
+  </si>
+  <si>
+    <t>计划人数</t>
   </si>
   <si>
     <t>备注</t>
@@ -31,28 +34,37 @@
     <t>1</t>
   </si>
   <si>
+    <t>F1</t>
+  </si>
+  <si>
     <t>1.1</t>
   </si>
   <si>
-    <t>1.2</t>
-  </si>
-  <si>
-    <t>1.2.3</t>
+    <t>A部门</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>2.1</t>
-  </si>
-  <si>
-    <t>2.2</t>
-  </si>
-  <si>
-    <t>2.2.3</t>
-  </si>
-  <si>
-    <t>2.3</t>
+    <t>F2</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>F3</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>F4</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>F5</t>
   </si>
 </sst>
 </file>
@@ -60,10 +72,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -88,6 +100,13 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color theme="3"/>
@@ -103,16 +122,24 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF0000FF"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -121,29 +148,6 @@
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -165,14 +169,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="等线"/>
@@ -189,17 +185,32 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF006100"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -212,14 +223,15 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -246,31 +258,115 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -282,145 +378,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -482,36 +494,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
@@ -546,147 +528,177 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="20" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="19" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="19" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -707,9 +719,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" quotePrefix="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1031,13 +1040,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D10"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="17.6" outlineLevelCol="3"/>
+  <dimension ref="A1:E10"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="17.6" outlineLevelCol="4"/>
   <cols>
     <col min="2" max="4" width="11" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:5">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1050,51 +1059,66 @@
       <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="2" spans="1:1">
-      <c r="A2" s="4" t="s">
-        <v>4</v>
+    <row r="2" spans="1:2">
+      <c r="A2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="4" t="s">
-        <v>5</v>
+    <row r="3" spans="1:2">
+      <c r="A3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:1">
-      <c r="A4" s="4" t="s">
-        <v>6</v>
+    <row r="4" spans="1:2">
+      <c r="A4" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:1">
+    <row r="5" spans="1:2">
       <c r="A5" s="3" t="s">
-        <v>7</v>
+        <v>11</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:1">
-      <c r="A6" s="4" t="s">
-        <v>8</v>
+    <row r="6" spans="1:2">
+      <c r="A6" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:1">
-      <c r="A7" s="4" t="s">
-        <v>9</v>
+    <row r="7" spans="1:2">
+      <c r="A7" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:1">
-      <c r="A8" s="4" t="s">
-        <v>10</v>
-      </c>
+      <c r="A8" s="3"/>
     </row>
     <row r="9" spans="1:1">
-      <c r="A9" s="3" t="s">
-        <v>11</v>
-      </c>
+      <c r="A9" s="3"/>
     </row>
     <row r="10" spans="1:1">
-      <c r="A10" s="4" t="s">
-        <v>12</v>
-      </c>
+      <c r="A10" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Ft-Cloud/ft-services/ft-service-pm/src/main/resources/template/importOrg.xlsx
+++ b/Ft-Cloud/ft-services/ft-service-pm/src/main/resources/template/importOrg.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="24320"/>
+    <workbookView windowWidth="30240" windowHeight="13860"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t>序号</t>
   </si>
@@ -65,6 +65,9 @@
   </si>
   <si>
     <t>F5</t>
+  </si>
+  <si>
+    <t>占位符</t>
   </si>
 </sst>
 </file>
@@ -72,10 +75,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -93,6 +96,14 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
@@ -107,23 +118,54 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="11"/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -137,40 +179,54 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
-      <sz val="13"/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color theme="1"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -178,60 +234,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -252,24 +255,132 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -282,7 +393,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -294,145 +405,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -470,15 +473,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
@@ -494,11 +488,41 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom style="medium">
         <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -520,6 +544,15 @@
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color theme="4"/>
       </top>
@@ -528,180 +561,150 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="20" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="19" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="14" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="19" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -1040,8 +1043,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E10"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="17.6" outlineLevelCol="4"/>
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="17.6" outlineLevelRow="7" outlineLevelCol="4"/>
   <cols>
     <col min="2" max="4" width="11" style="1"/>
   </cols>
@@ -1111,14 +1114,10 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:1">
-      <c r="A8" s="3"/>
-    </row>
-    <row r="9" spans="1:1">
-      <c r="A9" s="3"/>
-    </row>
-    <row r="10" spans="1:1">
-      <c r="A10" s="3"/>
+    <row r="8" spans="2:2">
+      <c r="B8" s="1" t="s">
+        <v>17</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Ft-Cloud/ft-services/ft-service-pm/src/main/resources/template/importOrg.xlsx
+++ b/Ft-Cloud/ft-services/ft-service-pm/src/main/resources/template/importOrg.xlsx
@@ -75,10 +75,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -90,50 +90,43 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF800080"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -149,7 +142,84 @@
     <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -163,78 +233,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -255,6 +255,150 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -267,19 +411,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -291,151 +423,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -460,6 +460,56 @@
       </top>
       <bottom style="thin">
         <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -507,57 +557,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -566,148 +566,148 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="42" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1120,6 +1120,12 @@
       </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D1048576">
+      <formula1>0</formula1>
+      <formula2>99999999999</formula2>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>
